--- a/demo/Results_chocolate/Posthoc.xlsx
+++ b/demo/Results_chocolate/Posthoc.xlsx
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.064172509016172</v>
+        <v>7.064172044837984</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03296831772498363</v>
+        <v>0.03296835827285992</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6.990662381005584</v>
+        <v>6.990661826914241</v>
       </c>
       <c r="F2" t="n">
-        <v>7.138455630861336</v>
+        <v>7.138455258548533</v>
       </c>
     </row>
     <row r="3">
@@ -479,10 +479,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.062157080310849</v>
+        <v>7.062156583008101</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03295892565345287</v>
+        <v>0.03295895216697083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -490,10 +490,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6.988667894154654</v>
+        <v>6.988667338069861</v>
       </c>
       <c r="F3" t="n">
-        <v>7.136419040415339</v>
+        <v>7.136418603192371</v>
       </c>
     </row>
   </sheetData>

--- a/demo/Results_chocolate/Posthoc.xlsx
+++ b/demo/Results_chocolate/Posthoc.xlsx
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.064172044837984</v>
+        <v>7.065067765735493</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03296835827285992</v>
+        <v>0.03377133663205902</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6.990661826914241</v>
+        <v>6.989776654556104</v>
       </c>
       <c r="F2" t="n">
-        <v>7.138455258548533</v>
+        <v>7.141169883003172</v>
       </c>
     </row>
     <row r="3">
@@ -479,10 +479,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.062156583008101</v>
+        <v>7.063096528158398</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03295895216697083</v>
+        <v>0.03376182454419493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -490,10 +490,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6.988667338069861</v>
+        <v>6.987826622525147</v>
       </c>
       <c r="F3" t="n">
-        <v>7.136418603192371</v>
+        <v>7.139177209301701</v>
       </c>
     </row>
   </sheetData>
